--- a/20260428_CONTROL STOCK ASA.xlsx
+++ b/20260428_CONTROL STOCK ASA.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Respuestas de formulario 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respuestas de formulario 1'!$A$1:$J$76</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respuestas de formulario 1'!$A$1:$J$89</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="209">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -561,6 +561,99 @@
   </si>
   <si>
     <t xml:space="preserve">Caja con terminales para cable sensor 3 y 4 pines hembra y macho </t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Motor se deriva a paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tv 75" Samsung </t>
+  </si>
+  <si>
+    <t>Tv tercer piso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispensadores </t>
+  </si>
+  <si>
+    <t>908391x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insumo de limpieza </t>
+  </si>
+  <si>
+    <t>Aire acondicionado clark</t>
+  </si>
+  <si>
+    <t>Incc -18here13</t>
+  </si>
+  <si>
+    <t>Aires con parte exterior incluida</t>
+  </si>
+  <si>
+    <t>Traje blanco servicio</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>Traje de servicio</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Ribbons 34mm X 770m</t>
+  </si>
+  <si>
+    <t>Correa dentada</t>
+  </si>
+  <si>
+    <t>C-2380TPCC</t>
+  </si>
+  <si>
+    <t>Nuevos tpc</t>
+  </si>
+  <si>
+    <t>Polea dentada</t>
+  </si>
+  <si>
+    <t>Nuevo tpc</t>
+  </si>
+  <si>
+    <t>Ventosas</t>
+  </si>
+  <si>
+    <t>C-2368WM</t>
+  </si>
+  <si>
+    <t>Caja reductora</t>
+  </si>
+  <si>
+    <t>C-2322HAM</t>
+  </si>
+  <si>
+    <t>Nuevo hamburgo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuchillos variovac </t>
+  </si>
+  <si>
+    <t>C-2389.1TPCC</t>
+  </si>
+  <si>
+    <t>Nuevos TPC</t>
+  </si>
+  <si>
+    <t>Rotary valve with motor for  silo1 und 7</t>
+  </si>
+  <si>
+    <t>C-2291wm</t>
+  </si>
+  <si>
+    <t>Repuestos ways</t>
   </si>
 </sst>
 </file>
@@ -701,8 +794,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J76" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$J$76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J89" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$J$89"/>
   <tableColumns count="10">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="NOMBRE" id="2"/>
@@ -917,6 +1010,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -3133,7 +3227,387 @@
         <v>177</v>
       </c>
     </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="4">
+        <v>46140.36623649306</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F77" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G77" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H77" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="4">
+        <v>46148.484369259255</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E78" s="5">
+        <v>1002.0</v>
+      </c>
+      <c r="F78" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G78" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="H78" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="4">
+        <v>46148.48595702546</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F79" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="G79" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="H79" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="4">
+        <v>46148.49119954861</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F80" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G80" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="H80" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="4">
+        <v>46148.505063425924</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F81" s="5">
+        <v>22.0</v>
+      </c>
+      <c r="G81" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="H81" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="4">
+        <v>46148.505787511574</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F82" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="G82" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="H82" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="4">
+        <v>46149.66090137731</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="G83" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H83" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="4">
+        <v>46149.663304560185</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F84" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G84" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H84" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="4">
+        <v>46149.66435670139</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G85" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H85" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="4">
+        <v>46149.665365196764</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="G86" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H86" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="4">
+        <v>46149.67060378472</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G87" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H87" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="4">
+        <v>46149.67221716435</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F88" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="G88" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H88" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="4">
+        <v>46149.67507539352</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F89" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G89" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="H89" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
